--- a/data/model_selection.xlsx
+++ b/data/model_selection.xlsx
@@ -824,7 +824,8 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>ONLY NE is good; SD explodes for TE</t>
+          <t xml:space="preserve">ONLY NE is good; SD explodes for TE
+2026-09-07 source review: NE identifies the detailed Ecopath model, not northeastern coverage. The study covers the whole Sea of Okhotsk, about 1,590,000 km² (Chaikina 2020, pp. 24–26).</t>
         </is>
       </c>
       <c r="J10" s="3" t="n">
@@ -1088,7 +1089,8 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>646 is the better of the two</t>
+          <t xml:space="preserve">646 is the better of the two
+2026-09-07 source review: the 1998 model covers 111,932 km² off the country Guinea (Guénette &amp; Diallo 2004, pp. 124–125). Coverage of the Guinea Current LME is not demonstrated; regional application is a geographic transfer.</t>
         </is>
       </c>
       <c r="J15" s="3" t="n">
@@ -1186,7 +1188,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07 source review: the payload is the 1980 model despite its 1963 filename/model_year. All 11 compared biomass entries match Christensen (1998), Table II p. 136, 1980; 10 disagree with 1963. Filename and parameter values are retained.</t>
+        </is>
+      </c>
       <c r="J17" s="3" t="n">
         <v>1</v>
       </c>
